--- a/sheets/조재수대금교본/검수/네박자.xlsx
+++ b/sheets/조재수대금교본/검수/네박자.xlsx
@@ -5929,7 +5929,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -6133,8 +6133,7 @@
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -6309,7 +6308,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K9" s="23"/>
@@ -6338,36 +6337,22 @@
     </row>
     <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K10" s="24"/>
@@ -6379,29 +6364,19 @@
       <c r="M10" s="24"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="S10" s="24"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
     <row r="11" ht="97.23" customHeight="true">
@@ -6433,7 +6408,7 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="K11" s="22"/>
@@ -6577,8 +6552,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -6614,8 +6588,7 @@
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q14" s="24"/>
@@ -6623,8 +6596,7 @@
       <c r="S14" s="24"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="U14" s="24"/>
@@ -6745,17 +6717,9 @@
       <c r="G18" s="24"/>
       <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L18" s="21"/>
       <c r="M18" s="24"/>
       <c r="N18" s="21" t="inlineStr">
         <is>
@@ -6822,7 +6786,7 @@
       <c r="O21" s="22"/>
       <c r="P21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅋ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q21" s="22"/>
@@ -6922,23 +6886,20 @@
       <c r="O24" s="24"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞c
-汰
-‹</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="S24" s="24"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑲·
-‹</t>
+          <t xml:space="preserve">㑲·</t>
         </is>
       </c>
       <c r="U24" s="24"/>
@@ -7032,7 +6993,7 @@
       <c r="Q27" s="23"/>
       <c r="R27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S27" s="23"/>
@@ -7059,16 +7020,11 @@
       <c r="M28" s="24"/>
       <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
       <c r="R28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S28" s="24"/>
@@ -7104,7 +7060,7 @@
       <c r="Q29" s="22"/>
       <c r="R29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="S29" s="22"/>
@@ -7193,8 +7149,7 @@
       <c r="O32" s="24"/>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="Q32" s="24"/>
@@ -7206,8 +7161,7 @@
       <c r="S32" s="24"/>
       <c r="T32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="U32" s="24"/>
@@ -7309,23 +7263,11 @@
       <c r="M36" s="24"/>
       <c r="N36" s="21"/>
       <c r="O36" s="24"/>
-      <c r="P36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P36" s="21"/>
       <c r="Q36" s="24"/>
-      <c r="R36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R36" s="21"/>
       <c r="S36" s="24"/>
-      <c r="T36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T36" s="21"/>
       <c r="U36" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/네박자.xlsx
+++ b/sheets/조재수대금교본/검수/네박자.xlsx
@@ -5929,7 +5929,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -6308,7 +6308,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㄴ</t>
         </is>
       </c>
       <c r="K9" s="23"/>
@@ -6408,7 +6408,7 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="K11" s="22"/>
@@ -6786,7 +6786,7 @@
       <c r="O21" s="22"/>
       <c r="P21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅋ</t>
         </is>
       </c>
       <c r="Q21" s="22"/>
@@ -6886,7 +6886,7 @@
       <c r="O24" s="24"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞c
 汰</t>
         </is>
       </c>
@@ -6993,7 +6993,7 @@
       <c r="Q27" s="23"/>
       <c r="R27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㄴ</t>
         </is>
       </c>
       <c r="S27" s="23"/>
@@ -7060,7 +7060,7 @@
       <c r="Q29" s="22"/>
       <c r="R29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="S29" s="22"/>

--- a/sheets/조재수대금교본/검수/네박자.xlsx
+++ b/sheets/조재수대금교본/검수/네박자.xlsx
@@ -5854,32 +5854,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="86.96" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="97.23" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="97.23" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="97.23" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="97.23" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="97.23" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="97.23" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="97.23" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="97.23" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -6379,7 +6379,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="97.23" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="97.23" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="97.23" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="97.23" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="97.23" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="97.23" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -6675,7 +6675,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="97.23" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -6698,7 +6698,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="97.23" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="86.96" customHeight="true">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="97.23" customHeight="true">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="97.23" customHeight="true">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="97.23" customHeight="true">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="97.23" customHeight="true">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="97.23" customHeight="true">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="97.23" customHeight="true">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="97.23" customHeight="true">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="97.23" customHeight="true">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="97.23" customHeight="true">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="97.23" customHeight="true">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="97.23" customHeight="true">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="97.23" customHeight="true">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="97.23" customHeight="true">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="97.23" customHeight="true">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -7224,7 +7224,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="97.23" customHeight="true">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -7247,7 +7247,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="97.23" customHeight="true">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -7277,7 +7277,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
